--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28223"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danielrp551\OneDrive\Documentos\TRABAJO\TRABAJO-CHATBOT\server_py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B71A59-B948-4312-B366-605B61F55CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9883F7A-C053-4EC7-8105-069AA69A0DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8985" yWindow="5100" windowWidth="16575" windowHeight="7605" xr2:uid="{DD16B0FA-D587-48E9-AF96-7ACB9E650AAA}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="14401" windowHeight="7283" xr2:uid="{DD16B0FA-D587-48E9-AF96-7ACB9E650AAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
